--- a/artfynd/A 25503-2022 artfynd.xlsx
+++ b/artfynd/A 25503-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 25503-2022 artfynd.xlsx
+++ b/artfynd/A 25503-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102716866</v>
+        <v>102716844</v>
       </c>
       <c r="B2" t="n">
-        <v>73678</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6439</v>
+        <v>1365</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567621.8005584385</v>
+        <v>568032</v>
       </c>
       <c r="R2" t="n">
-        <v>7191224.714917043</v>
+        <v>7191556</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Lokalen precis sönderkörd av skogsmaskin</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>102716865</v>
+        <v>102716866</v>
       </c>
       <c r="B3" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>6439</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567621.8005584385</v>
+        <v>567622</v>
       </c>
       <c r="R3" t="n">
-        <v>7191224.714917043</v>
+        <v>7191225</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -902,12 +897,7 @@
         <v>102716863</v>
       </c>
       <c r="B4" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567621.8197287706</v>
+        <v>567622</v>
       </c>
       <c r="R4" t="n">
-        <v>7191223.863781647</v>
+        <v>7191224</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1008,6 +998,667 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>102716865</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>V Nästansjö, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>567622</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7191225</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-08-05</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-08-05</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>102716860</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>V Nästansjö, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>567730</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7191335</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-08-05</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-08-05</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>102716842</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>V Nästansjö, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>568020</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7191593</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-08-05</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-08-05</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>102716845</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>V Nästansjö, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>567953</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7191545</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-08-05</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-08-05</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>102716861</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>V Nästansjö, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>567732</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7191335</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-08-05</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-08-05</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>102716846</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>V Nästansjö, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>567950</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7191549</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-08-05</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-08-05</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
